--- a/tests/fixtures/table/book.xlsx
+++ b/tests/fixtures/table/book.xlsx
@@ -27,6 +27,10 @@
   </si>
   <si>
     <t>東京</t>
+    <rPh sb="0" eb="2">
+      <t>トウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>大阪</t>
